--- a/file_mau.xlsx
+++ b/file_mau.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
   <si>
     <t>Mã</t>
   </si>
@@ -43,9 +43,6 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Dịch vụ</t>
-  </si>
-  <si>
     <t>Ngày bắt đầu</t>
   </si>
   <si>
@@ -55,21 +52,6 @@
     <t>Deadline</t>
   </si>
   <si>
-    <t>Người tạo</t>
-  </si>
-  <si>
-    <t>Ngày tạo</t>
-  </si>
-  <si>
-    <t>Ngày update</t>
-  </si>
-  <si>
-    <t>Trạng thái</t>
-  </si>
-  <si>
-    <t>Thao tác</t>
-  </si>
-  <si>
     <t>T1</t>
   </si>
   <si>
@@ -88,9 +70,6 @@
     <t>Ghi chú nếu có</t>
   </si>
   <si>
-    <t>Common service</t>
-  </si>
-  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -100,15 +79,6 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Trần Nguyên Phi</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>Đang xử lý</t>
-  </si>
-  <si>
     <t>Sub-task</t>
   </si>
   <si>
@@ -124,9 +94,6 @@
     <t>Gắn vào task đã tồn tại</t>
   </si>
   <si>
-    <t>SmartTV - App HTML5</t>
-  </si>
-  <si>
     <t>Cot</t>
   </si>
   <si>
@@ -154,9 +121,6 @@
     <t>note - map vao JIRA_FIELD_NOTE</t>
   </si>
   <si>
-    <t>service_name - map vao JIRA_FIELD_SERVICE</t>
-  </si>
-  <si>
     <t>start_date - map vao JIRA_FIELD_TARGET_START</t>
   </si>
   <si>
@@ -164,12 +128,6 @@
   </si>
   <si>
     <t>deadline/duedate</t>
-  </si>
-  <si>
-    <t>Cot theo doi noi bo, tool khong gui len Jira</t>
-  </si>
-  <si>
-    <t>MYTVB2C-52104</t>
   </si>
 </sst>
 </file>
@@ -538,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -547,15 +505,10 @@
     <col min="4" max="4" width="45" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="8" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,134 +539,80 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -728,7 +627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -737,10 +636,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -748,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -756,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -764,7 +663,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -772,7 +671,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -780,7 +679,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -788,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -796,7 +695,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -804,7 +703,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -812,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -820,55 +719,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/file_mau.xlsx
+++ b/file_mau.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
   <si>
     <t>Mã</t>
   </si>
@@ -91,6 +91,9 @@
     <t>2026-07-08</t>
   </si>
   <si>
+    <t>MYTVB2C-50784</t>
+  </si>
+  <si>
     <t>Gắn vào task đã tồn tại</t>
   </si>
   <si>
@@ -112,7 +115,7 @@
     <t>title/summary - bat buoc</t>
   </si>
   <si>
-    <t>assignee - username Jira, bat buoc</t>
+    <t>assignee - username Jira; de trong thi lay JIRA_USERNAME</t>
   </si>
   <si>
     <t>description</t>
@@ -600,10 +603,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -636,10 +639,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -647,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -655,7 +658,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -663,7 +666,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -671,7 +674,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -679,7 +682,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -687,7 +690,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -695,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -703,7 +706,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -711,7 +714,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -719,7 +722,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
